--- a/testakten/filmrechte-sicherungsuebertragung-insolvenz-schwetzingen/06_Insolvenz_AssetDeal/05_Closing_Checkliste.xlsx
+++ b/testakten/filmrechte-sicherungsuebertragung-insolvenz-schwetzingen/06_Insolvenz_AssetDeal/05_Closing_Checkliste.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Closing" sheetId="1" r:id="Re00f9e6ea8684f32"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Uebergabe" sheetId="2" r:id="R33e4c4a50e574185"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Closing" sheetId="1" r:id="R23a6ad9ed8124055"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Uebergabe" sheetId="2" r:id="R5d09648fcd944a2a"/>
   </x:sheets>
 </x:workbook>
 </file>
